--- a/data/WP18_sachgebiete_fraktionslos.xlsx
+++ b/data/WP18_sachgebiete_fraktionslos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">Sachgebiet</t>
   </si>
@@ -27,9 +27,6 @@
   </si>
   <si>
     <t xml:space="preserve">Verspätet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pünktlichkeitsquote</t>
   </si>
   <si>
     <t xml:space="preserve">Gesellschaft, Bevölkerung</t>
@@ -389,13 +386,10 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
         <v>18</v>
@@ -408,14 +402,11 @@
       </c>
       <c r="E2" t="n">
         <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
         <v>18</v>
@@ -428,14 +419,11 @@
       </c>
       <c r="E3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
         <v>18</v>
@@ -448,14 +436,11 @@
       </c>
       <c r="E4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
         <v>18</v>
@@ -468,14 +453,11 @@
       </c>
       <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
         <v>18</v>
@@ -488,9 +470,6 @@
       </c>
       <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -727,13 +706,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531B2EF6-7CD5-4CA9-B73A-9697EEAFF86D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{977AEE1B-DB1A-4DDE-9945-17ABB482FC79}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6107193A-CC15-4CF4-8E8C-78EB9FA0AFD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59399A83-CC94-4180-8F45-894995F89188}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAB1B719-57AA-4C2E-B866-4B3B4388632A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8EB8A13-1E65-41BA-A710-DCB7E62B4223}"/>
 </file>